--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -1691,7 +1691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1902,156 +1902,303 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>接纳版本</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>本次接纳的版本号</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>如 V1.0;修订后递增</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>是否接纳</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>枚举(单选)</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>是否接纳该改进项</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>是/否;否→流程终止</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>不接纳理由</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>条件必填</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>不接纳的原因说明</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>是否接纳为『否』时必填;接纳则留空</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>不接纳理由</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>不接纳的原因说明</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>是否接纳为『否』时必填;接纳则留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>闭环方法</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>枚举(单选)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>接纳后走哪条闭环</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>问题单闭环/需求闭环;决定生成哪类闭环单</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>计划完成期限</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>接纳后计划完成日期</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>由分析阶段接纳后给出</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>三、闭环单号(必填,需校验合法性)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>问题单号/需求单号</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>承接的闭环单号</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>需校验编号合法性(格式正确且单据真实存在);校验通过方可进入闭环阶段</t>
         </is>
       </c>
     </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>四、分析进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>表格列</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>进展条目序号</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>系统自增</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>本条进展内容描述</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>每条可单独提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>本条提交时间</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>系统取提交时当前时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>人员(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>提交人工号与姓名(成对)</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>系统取当前登录人</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2063,7 +2210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2352,12 +2499,132 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>表格列</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>进展条目序号</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>系统自增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>本条进展内容描述</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>每条可单独提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>本条提交时间</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>系统取提交时当前时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>人员(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>提交人工号与姓名(成对)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>系统取当前登录人</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2369,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2658,12 +2925,132 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>表格列</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>进展条目序号</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>系统自增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>本条进展内容描述</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>每条可单独提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>本条提交时间</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>系统取提交时当前时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>人员(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>提交人工号与姓名(成对)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>系统取当前登录人</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -1899,15 +1899,15 @@
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>接纳版本</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>如 V1.0;修订后递增</t>
+          <t>是否接纳为『是』时必填(如 V1.0);不接纳则留空</t>
         </is>
       </c>
     </row>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -1986,9 +1986,9 @@
           <t>闭环方法</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>问题单闭环/需求闭环;决定生成哪类闭环单</t>
+          <t>是否接纳为『是』时必填;问题单闭环/需求闭环</t>
         </is>
       </c>
     </row>
@@ -2013,9 +2013,9 @@
           <t>计划完成期限</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -2030,14 +2030,14 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>由分析阶段接纳后给出</t>
+          <t>是否接纳为『是』时必填</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>三、闭环单号(必填,需校验合法性)</t>
+          <t>三、闭环单号(接纳后必填,需校验合法性)</t>
         </is>
       </c>
       <c r="B16" s="9" t="n"/>
@@ -2051,9 +2051,9 @@
           <t>问题单号/需求单号</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>需校验编号合法性(格式正确且单据真实存在);校验通过方可进入闭环阶段</t>
+          <t>是否接纳为『是』时必填;需校验编号合法性(格式正确且单据真实存在),校验通过方可进入闭环阶段</t>
         </is>
       </c>
     </row>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -13,8 +13,7 @@
     <sheet name="3-分析-改进项分析单" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="4-1闭环-问题单闭环单" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="4-2闭环-需求闭环单" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5-1-子项验收单" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="5-2-总项验收单" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5-验收-验收单" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,14 +90,8 @@
       <color rgb="00806000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="005B2C6F"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -135,11 +128,6 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4DFEC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -167,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -205,9 +193,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -575,12 +560,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C21"/>
+  <dimension ref="B1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -653,7 +638,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>绿字绿底 —— 系统自动生成/继承,用户免填(编号/状态/关联继承/派生计数/固定路由值/部分日期/验收人)</t>
+          <t>绿字绿底 —— 系统自动生成/继承,用户免填(编号/状态/关联/日期/责任人继承/提交人等)</t>
         </is>
       </c>
     </row>
@@ -665,7 +650,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>紫字紫底 —— 系统预填默认值(如审批人=提出人),用户可修改</t>
+          <t>紫字紫底 —— 系统预填默认值,用户可修改</t>
         </is>
       </c>
     </row>
@@ -689,115 +674,91 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>引用其他单据的编号,通常由系统从父单继承</t>
+          <t>引用其他单据/系统的编号,多由系统继承(如关联yw系统单号需用户填写)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>字段类型 · 文本</t>
+          <t>字段类型 · 文本 / 长文本</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>简短文字</t>
+          <t>简短文字 / 多行描述</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>字段类型 · 长文本</t>
+          <t>字段类型 · 日期 / 日期·时长</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>多行描述</t>
+          <t>日期(YYYY-MM-DD);SLA时间可为日期或时长</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>字段类型 · 日期</t>
+          <t>字段类型 · 枚举(单选)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>日期,建议 YYYY-MM-DD</t>
+          <t>下拉单选,可选值固定(审批人为固定名单)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>字段类型 · 数字</t>
+          <t>字段类型 · 富文本(可粘贴图片)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>支持富文本与粘贴图片(闭环自测/验收结论)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>字段类型 · 枚举(单选)</t>
+          <t>字段类型 · 人员(工号+姓名)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>下拉单选,可选值固定</t>
+          <t>工号与姓名成对录入</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>字段类型 · 签批(人+日期)</t>
+          <t>字段类型 · 表格列</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>责任人签字 + 日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>字段类型 · 表格列</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>子项明细/拆单分发表中的列</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>字段类型 · 人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>工号与姓名成对录入</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="50" customHeight="1">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>每张单据各占一个 Sheet。本表为精简审核版:已按反馈去除冗余字段,并将系统能自动生成/继承的字段单独标为『系统生成』(用户免填)。确认后可据此把校验落到正式表单。</t>
+          <t>进展子项表中的列</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>单链流程(不拆子项):提出 → 评审 → 改进项分析 → 闭环 → 验收。关键规则:①评审完成前提出单可编辑;②评审不通过打回提出、分析不接纳打回评审;③责任人 评审填写→分析继承→闭环继承;④谁提出谁验收,不可转单。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="30">
     <mergeCell ref="C8"/>
     <mergeCell ref="B9"/>
     <mergeCell ref="C17"/>
@@ -806,10 +767,7 @@
     <mergeCell ref="B6"/>
     <mergeCell ref="B5"/>
     <mergeCell ref="C13"/>
-    <mergeCell ref="C19"/>
     <mergeCell ref="B4"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C18"/>
     <mergeCell ref="B7"/>
     <mergeCell ref="C15"/>
     <mergeCell ref="B16"/>
@@ -819,7 +777,7 @@
     <mergeCell ref="C5"/>
     <mergeCell ref="C4"/>
     <mergeCell ref="B12"/>
-    <mergeCell ref="B18"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B11"/>
     <mergeCell ref="C10"/>
     <mergeCell ref="C16"/>
@@ -831,7 +789,6 @@
     <mergeCell ref="C12"/>
     <mergeCell ref="C11"/>
     <mergeCell ref="B10"/>
-    <mergeCell ref="B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -843,14 +800,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -863,7 +820,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>主单号 QI-YYYY-NNN    ①提出 → ②评审 → ③分析 → ④闭环 → ⑤验收</t>
+          <t>主单号 QI-YYYY-NNN    ①提出 → ②评审 → ③改进项分析 → ④闭环 → ⑤验收</t>
         </is>
       </c>
     </row>
@@ -959,7 +916,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>当前状态</t>
@@ -982,7 +939,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>初始默认『待评审』;8 态状态机</t>
+          <t>初始默认『待评审』</t>
         </is>
       </c>
     </row>
@@ -1092,72 +1049,72 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>关联yw系统单号</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>关联</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>来源对应的yw系统单号</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>需关联来源业务系统的原始单号</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>总体背景与目标</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>长文本</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>问题概述、影响、期望达成</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>四、改进子项明细(表格,逐行一个子项)</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-    </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>子项编号</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>主单内子项序号</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>01/02/03…;可增行</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>四、审批</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>子项标题</t>
+          <t>审批人</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -1167,145 +1124,25 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>表格列</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>子项名称</t>
+          <t>审批人(固定名单)</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>子项性质</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>问题单/需求;评审据此拆单</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>子项简述/现象</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>现象/问题描述</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>处理优先级</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>高/中/低</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>五、审批</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>审批人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>审批人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>固定下拉名单,由系统配置;评审人=审批人</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A8:E8"/>
@@ -1320,14 +1157,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1340,7 +1177,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联主诉求单号    评审通过则生成子单进入分析,不通过则流程终止</t>
+          <t>关联主诉求单号    评审通过则进入分析并指派责任人;不通过则打回提出人修改</t>
         </is>
       </c>
     </row>
@@ -1469,9 +1306,9 @@
           <t>评审人(工号+姓名)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1493,7 +1330,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>二、子项拆单分发表(逐项评审;子项内容继承自提出单,此处只判定通过与否)</t>
+          <t>二、评审结论</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
@@ -1504,58 +1341,58 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>子项编号</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>评审结果</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>表格列</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>承接提出单子项(子项内容随编号继承,无需重填)</t>
+          <t>本次评审结论</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
+          <t>通过/不通过;不通过则打回提出人</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>评审结果</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>责任人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>表格列</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>该子项评审结论</t>
+          <t>改进项责任人</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>通过/不通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+          <t>评审结果为『通过』时必填;分析/闭环责任人由此继承</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>不通过理由</t>
@@ -1568,7 +1405,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>表格列</t>
+          <t>长文本</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1578,107 +1415,15 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>评审结果为『不通过』时必填;通过则留空</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>生成子单号</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>评审生成子单号</t>
-        </is>
-      </c>
-      <c r="E13" s="12">
-        <f> 主单号+子项序号;仅评审通过时生成</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>责任人/部门</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>条件必填</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>该子项责任人及部门</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>评审结果为『通过』时必填;不通过则无需指定</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>二(续)、统计</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>拆单总数(张)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>数字</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>生成子单数量</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>系统按分发表行数统计</t>
+          <t>评审结果为『不通过』时必填</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1696,9 +1441,9 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1711,7 +1456,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联:子单号 + 父诉求单号    接纳后填写闭环单号(校验合法性)方可进入闭环;不接纳则终止</t>
+          <t>关联:主诉求单号    接纳后填写闭环单号(校验合法性)进入闭环;不接纳则打回评审</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1528,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>关联子单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1798,7 +1543,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>所属子单</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -1810,7 +1555,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>分析日期</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1820,24 +1565,24 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
+          <t>分析提交日期</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>系统继承</t>
+          <t>系统取提交分析表单时当前日期</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>分析日期</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -1847,44 +1592,44 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>分析提交日期</t>
+          <t>单据状态</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>系统取提交分析表单时当前日期</t>
+          <t>默认『分析中』</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>责任人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>单据状态</t>
+          <t>改进项责任人</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>默认『分析中』</t>
+          <t>系统继承自评审阶段填写的责任人</t>
         </is>
       </c>
     </row>
@@ -1949,7 +1694,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>是/否;否→流程终止</t>
+          <t>是/否;否→打回评审阶段</t>
         </is>
       </c>
     </row>
@@ -2210,14 +1955,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2230,7 +1975,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联:子单号 + 父诉求单号 + 分析单号    只关注当前进展与闭环效果自测</t>
+          <t>关联:主诉求单号 + 分析单号    关注当前进展与闭环效果自测</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2047,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>关联子单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -2317,7 +2062,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>所属子单</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -2329,7 +2074,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>关联分析单号</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -2344,7 +2089,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
+          <t>承接分析单</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -2356,7 +2101,7 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>关联分析单号</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2366,24 +2111,24 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>承接分析单</t>
+          <t>单据状态</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>系统继承</t>
+          <t>默认『实施中』</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>闭环类型</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -2393,226 +2138,253 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>单据状态</t>
+          <t>闭环路径</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>默认『实施中』</t>
+          <t>固定『问题单闭环』</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>闭环类型</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>责任人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>闭环路径</t>
+          <t>改进项责任人</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>固定『问题单闭环』</t>
+          <t>系统继承自分析阶段责任人</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SLA时间</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>日期/时长</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>闭环完成时限</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>由闭环责任人填写并可修改</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>二、进展与自测</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>当前进展</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>当前实施进展描述</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>当前进展</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>当前实施进展描述</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>闭环效果自测</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>富文本(可粘贴图片)</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>自测的闭环效果</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>支持富文本与粘贴图片</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>进展条目序号</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>系统自增</t>
-        </is>
-      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>长文本</t>
+          <t>表格列</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>本条进展内容描述</t>
+          <t>进展条目序号</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>每条可单独提交</t>
+          <t>系统自增</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>长文本</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>本条提交时间</t>
+          <t>本条进展内容描述</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>系统取提交时当前时间</t>
+          <t>每条可单独提交</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>本条提交时间</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>系统取提交时当前时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>提交人</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>人员(工号+姓名)</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>提交人工号与姓名(成对)</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>系统取当前登录人</t>
         </is>
@@ -2620,11 +2392,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2636,14 +2408,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2656,7 +2428,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联:子单号 + 父诉求单号 + 分析单号    只关注当前进展与闭环效果自测</t>
+          <t>关联:主诉求单号 + 分析单号    关注当前进展与闭环效果自测</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2500,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>关联子单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -2743,7 +2515,7 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>所属子单</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -2755,7 +2527,7 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>关联分析单号</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -2770,7 +2542,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
+          <t>承接分析单</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -2782,7 +2554,7 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>关联分析单号</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2792,24 +2564,24 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>承接分析单</t>
+          <t>单据状态</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>系统继承</t>
+          <t>默认『实施中』</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>闭环类型</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -2819,226 +2591,253 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>文本</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>单据状态</t>
+          <t>闭环路径</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>默认『实施中』</t>
+          <t>固定『需求闭环』</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>闭环类型</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>责任人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>闭环路径</t>
+          <t>改进项责任人</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>固定『需求闭环』</t>
+          <t>系统继承自分析阶段责任人</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SLA时间</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>日期/时长</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>闭环完成时限</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>由闭环责任人填写并可修改</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>二、进展与自测</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>当前进展</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>当前实施进展描述</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>当前进展</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>当前实施进展描述</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>闭环效果自测</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>富文本(可粘贴图片)</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>自测的闭环效果</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>支持富文本与粘贴图片</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>进展条目序号</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>系统自增</t>
-        </is>
-      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>长文本</t>
+          <t>表格列</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>本条进展内容描述</t>
+          <t>进展条目序号</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>每条可单独提交</t>
+          <t>系统自增</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>长文本</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>本条提交时间</t>
+          <t>本条进展内容描述</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>系统取提交时当前时间</t>
+          <t>每条可单独提交</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>本条提交时间</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>系统取提交时当前时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>提交人</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>人员(工号+姓名)</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>提交人工号与姓名(成对)</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>系统取当前登录人</t>
         </is>
@@ -3046,11 +2845,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3062,27 +2861,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5-1-子项验收单</t>
+          <t>5-验收-验收单</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联:子单号 + 父诉求单号 + 闭环单号    针对单张子单验收;全部子单通过后进入总项验收</t>
+          <t>关联:主诉求单号 + 闭环单号    验收人=改进提出人,不可转单</t>
         </is>
       </c>
     </row>
@@ -3142,7 +2941,7 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>子项验收单唯一编号</t>
+          <t>验收单唯一编号</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -3154,7 +2953,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>关联子单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -3169,19 +2968,19 @@
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>所属子单</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>系统继承</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>父诉求单号</t>
+          <t>关联闭环单号</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -3196,19 +2995,19 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
+          <t>承接的闭环单</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
+          <t>系统继承</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>关联闭环单号</t>
+          <t>验收人</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -3218,89 +3017,88 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>承接的闭环单</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>验收人工号与姓名(成对)</t>
+        </is>
+      </c>
+      <c r="E8" s="12">
+        <f>改进提出人,系统生成,锁定不可转单</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>验收人</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>预填(可改)</t>
+          <t>当前状态</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>人员(工号+姓名)</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>验收人工号与姓名(成对)</t>
+          <t>单据状态</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>系统预填为改进项提出人,可修改</t>
+          <t>默认『待验收』</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>单据状态</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>默认『待验收』</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>二、验收结论</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>二、验收结论</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>验收结论</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>富文本(可粘贴图片)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>验收结论说明</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>支持富文本与粘贴图片</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>验收结论</t>
+          <t>验收是否通过</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -3310,344 +3108,26 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>长文本</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>该子项验收结论说明</t>
+          <t>是否通过验收</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>验收是否通过</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>该子项是否通过验收</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>通过/不通过</t>
+          <t>通过/不通过;通过即完成</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A4:E4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>5-2-总项验收单</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>关联:主诉求单号    主单下全部子项验收通过后进行总项验收,通过即完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>字段名</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>填写要求</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>字段类型</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>详细信息</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>特殊要求</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>一、单据信息</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>总项验收单号</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>总项验收单唯一编号</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>系统生成,关联主单</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>关联主诉求单号</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>关联</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>所属主诉求单</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>系统继承</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>验收人</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>预填(可改)</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>验收人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>系统预填为改进项提出人,可修改</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>单据状态</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>默认『待总项验收』</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>二、子项验收状态(系统生成,只读)</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-    </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>各子项验收状态</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>本主单下各子项的验收是否通过</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>系统生成;列出每个子项编号及验收结果(通过/不通过/待验收),供总项验收参考</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>三、总项验收结论</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>总项验收结论</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>总项验收结论说明</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>总项验收是否通过</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>主单总项是否通过</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>通过/不通过;通过即完成</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -995,7 +995,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>诉求总体标题</t>
+          <t>诉求标题</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>诉求来源</t>
+          <t>关联运维系统单号</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
@@ -1032,24 +1032,24 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>关联</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>诉求来源渠道</t>
+          <t>关联的运维系统单号</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>现网问题 / 客户提出 / 实验室发现</t>
+          <t>运维单号即可,无需另填诉求来源</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>关联yw系统单号</t>
+          <t>诉求描述</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -1059,82 +1059,55 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>富文本(可粘贴图片)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>来源对应的yw系统单号</t>
+          <t>问题概述、影响、期望达成</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>需关联来源业务系统的原始单号</t>
+          <t>支持富文本与粘贴图片</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>总体背景与目标</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>四、评审人</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>评审人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>问题概述、影响、期望达成</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>四、审批</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>审批人</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>枚举(单选)</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>审批人(固定名单)</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>固定下拉名单,由系统配置;评审人=审批人</t>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>评审人(固定名单)</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>固定下拉名单,由系统配置;表单二评审人继承此项</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1115,7 @@
   <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A8:E8"/>
@@ -1300,15 +1273,15 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>评审人(工号+姓名)</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1323,7 +1296,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>系统继承提出单审批人(评审与审批为同一人)</t>
+          <t>系统继承提出单填写的评审人</t>
         </is>
       </c>
     </row>
@@ -1612,9 +1585,9 @@
           <t>责任人(工号+姓名)</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -2158,9 +2131,9 @@
           <t>责任人(工号+姓名)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -2611,9 +2584,9 @@
           <t>责任人(工号+姓名)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -1409,7 +1409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1726,139 +1726,139 @@
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>计划完成期限</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>三、闭环单号(接纳后必填,需校验合法性)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>问题单号/需求单号</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>条件必填</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>接纳后计划完成日期</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>是否接纳为『是』时必填</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>三、闭环单号(接纳后必填,需校验合法性)</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="42" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>问题单号/需求单号</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>条件必填</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>承接的闭环单号</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>是否接纳为『是』时必填;需校验编号合法性(格式正确且单据真实存在),校验通过方可进入闭环阶段</t>
         </is>
       </c>
     </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>四、分析进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+    </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>四、分析进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>表格列</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>进展条目序号</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>系统自增</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>表格列</t>
+          <t>长文本</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>进展条目序号</t>
+          <t>本条进展内容描述</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>系统自增</t>
+          <t>每条可单独提交</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>长文本</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>本条进展内容描述</t>
+          <t>本条提交时间</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>每条可单独提交</t>
+          <t>系统取提交时当前时间</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>提交时间</t>
+          <t>提交人</t>
         </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1868,42 +1868,15 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>本条提交时间</t>
+          <t>提交人工号与姓名(成对)</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>系统取提交时当前时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>提交人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>系统取当前登录人</t>
         </is>
@@ -1913,10 +1886,10 @@
   <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -11,9 +11,8 @@
     <sheet name="1-提出-质量改进诉求单" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2-评审-评审记录单" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="3-分析-改进项分析单" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="4-1闭环-问题单闭环单" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="4-2闭环-需求闭环单" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="5-验收-验收单" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="4-闭环单" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5-验收-验收单" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1914,14 +1913,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4-1闭环-问题单闭环单</t>
+          <t>4-闭环单</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联:主诉求单号 + 分析单号    关注当前进展与闭环效果自测</t>
+          <t>关联:主诉求单号 + 分析单号    由闭环方式决定单号前缀(PC-问题单/RC-需求)</t>
         </is>
       </c>
     </row>
@@ -1966,61 +1965,61 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>问题单号</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>闭环方式</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
+          <t>枚举(单选)</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>闭环路径</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>问题单闭环/需求闭环;决定单号前缀</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>闭环单号</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>问题闭环单唯一编号</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>PC-YYYY-NNN;系统生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>关联主诉求单号</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>关联</t>
-        </is>
-      </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
+          <t>闭环单唯一编号</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>系统继承</t>
+          <t>系统生成;前缀随闭环方式:PC-YYYY-NNN(问题单)/RC-YYYY-NNN(需求)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>关联分析单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -2035,7 +2034,7 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>承接分析单</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -2047,7 +2046,7 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>关联分析单号</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2057,24 +2056,24 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>关联</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>单据状态</t>
+          <t>承接分析单</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>默认『实施中』</t>
+          <t>系统继承</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>闭环类型</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -2084,17 +2083,17 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>文本</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>闭环路径</t>
+          <t>单据状态</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>固定『问题单闭环』</t>
+          <t>默认『实施中』</t>
         </is>
       </c>
     </row>
@@ -2354,459 +2353,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>4-2闭环-需求闭环单</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>关联:主诉求单号 + 分析单号    关注当前进展与闭环效果自测</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>字段名</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>填写要求</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>字段类型</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>详细信息</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>特殊要求</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>一、单据信息</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>需求单号</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>需求闭环单唯一编号</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>RC-YYYY-NNN;系统生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>关联主诉求单号</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>关联</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>所属主诉求单</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>系统继承</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>关联分析单号</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>关联</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>承接分析单</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>系统继承</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>单据状态</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>默认『实施中』</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>闭环类型</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>闭环路径</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>固定『需求闭环』</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>责任人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>改进项责任人</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>系统继承自分析阶段责任人</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>SLA时间</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>日期/时长</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>闭环完成时限</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>由闭环责任人填写并可修改</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>二、进展与自测</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>当前进展</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>当前实施进展描述</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>闭环效果自测</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>富文本(可粘贴图片)</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>自测的闭环效果</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>支持富文本与粘贴图片</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>进展条目序号</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>系统自增</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>本条进展内容描述</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>每条可单独提交</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>本条提交时间</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>系统取提交时当前时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>提交人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>系统取当前登录人</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -1968,9 +1968,9 @@
           <t>闭环方式</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>问题单闭环/需求闭环;决定单号前缀</t>
+          <t>系统继承自分析阶段的闭环方法;决定单号前缀</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>系统生成;前缀随闭环方式:PC-YYYY-NNN(问题单)/RC-YYYY-NNN(需求)</t>
+          <t>系统继承自分析阶段的问题单号/需求单号;前缀:PC-问题单/RC-需求</t>
         </is>
       </c>
     </row>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -1900,7 +1900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2165,7 +2165,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>当前进展</t>
+          <t>闭环效果自测</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
@@ -2175,116 +2175,116 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>长文本</t>
+          <t>富文本(可粘贴图片)</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>当前实施进展描述</t>
+          <t>自测的闭环效果</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>支持富文本与粘贴图片</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>闭环效果自测</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>富文本(可粘贴图片)</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>自测的闭环效果</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>支持富文本与粘贴图片</t>
-        </is>
-      </c>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>表格列</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>进展条目序号</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>系统自增</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>表格列</t>
+          <t>长文本</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>进展条目序号</t>
+          <t>本条进展内容描述</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>系统自增</t>
+          <t>每条可单独提交</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>长文本</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>本条进展内容描述</t>
+          <t>本条提交时间</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>每条可单独提交</t>
+          <t>系统取提交时当前时间</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>提交时间</t>
+          <t>提交人</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -2294,42 +2294,15 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>本条提交时间</t>
+          <t>提交人工号与姓名(成对)</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>系统取提交时当前时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>提交人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>系统取当前登录人</t>
         </is>
@@ -2340,8 +2313,8 @@
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2560,7 +2533,7 @@
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>验收结论</t>
@@ -2583,11 +2556,11 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>支持富文本与粘贴图片</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
+          <t>支持富文本与粘贴图片;不通过时截图贴入结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>验收是否通过</t>
@@ -2610,7 +2583,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>通过/不通过;通过即完成</t>
+          <t>通过/不通过;不通过则打回闭环阶段</t>
         </is>
       </c>
     </row>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1194,7 +1194,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>评审单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1204,24 +1204,24 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>编号</t>
+          <t>关联</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>评审单唯一编号</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>系统生成</t>
+          <t>系统从主单继承</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>关联主诉求单号</t>
+          <t>评审日期</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
+          <t>评审提交日期</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>系统从主单继承</t>
+          <t>系统取提交评审表单时当前日期</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>评审日期</t>
+          <t>评审人(工号+姓名)</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1258,89 +1258,89 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>评审提交日期</t>
+          <t>评审人工号与姓名(成对)</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>系统取提交评审表单时当前日期</t>
+          <t>系统继承提出单填写的评审人</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>评审人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>评审人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>系统继承提出单填写的评审人</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>二、评审结论</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>评审结果</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>枚举(单选)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>本次评审结论</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>通过/不通过;不通过则打回提出人</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>评审结果</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>责任人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>本次评审结论</t>
+          <t>改进项责任人</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>通过/不通过;不通过则打回提出人</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>评审结果为『通过』时必填;分析/闭环责任人由此继承</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>责任人(工号+姓名)</t>
+          <t>不通过理由</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1350,42 +1350,15 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>人员(工号+姓名)</t>
+          <t>长文本</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>改进项责任人</t>
+          <t>不通过的原因说明</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>评审结果为『通过』时必填;分析/闭环责任人由此继承</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>不通过理由</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>条件必填</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>不通过的原因说明</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>评审结果为『不通过』时必填</t>
         </is>
@@ -1396,505 +1369,13 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>3-分析-改进项分析单</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>关联:主诉求单号    接纳后填写闭环单号(校验合法性)进入闭环;不接纳则打回评审</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>字段名</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>填写要求</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>字段类型</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>详细信息</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>特殊要求</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>一、单据信息</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>分析单号</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>分析单唯一编号</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>AN-YYYY-NNN;系统生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>关联主诉求单号</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>关联</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>所属主诉求单</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>系统继承</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>分析日期</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>分析提交日期</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>系统取提交分析表单时当前日期</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>单据状态</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>默认『分析中』</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>责任人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>改进项责任人</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>系统继承自评审阶段填写的责任人</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>二、分析与接纳</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>接纳版本</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>条件必填</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>本次接纳的版本号</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>是否接纳为『是』时必填(如 V1.0);不接纳则留空</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>是否接纳</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>是否接纳该改进项</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>是/否;否→打回评审阶段</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>不接纳理由</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>条件必填</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>不接纳的原因说明</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>是否接纳为『否』时必填;接纳则留空</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>闭环方法</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>条件必填</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>接纳后走哪条闭环</t>
-        </is>
-      </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>是否接纳为『是』时必填;问题单闭环/需求闭环</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>三、闭环单号(接纳后必填,需校验合法性)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="42" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>问题单号/需求单号</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>条件必填</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>承接的闭环单号</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>是否接纳为『是』时必填;需校验编号合法性(格式正确且单据真实存在),校验通过方可进入闭环阶段</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>四、分析进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>进展条目序号</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>系统自增</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D19" s="12" t="inlineStr">
-        <is>
-          <t>本条进展内容描述</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>每条可单独提交</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>本条提交时间</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>系统取提交时当前时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>提交人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>系统取当前登录人</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A17:E17"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1913,14 +1394,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4-闭环单</t>
+          <t>3-分析-改进项分析单</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联:主诉求单号 + 分析单号    由闭环方式决定单号前缀(PC-问题单/RC-需求)</t>
+          <t>关联:主诉求单号    接纳后进入闭环;不接纳则打回评审</t>
         </is>
       </c>
     </row>
@@ -1962,10 +1443,10 @@
       <c r="D4" s="9" t="n"/>
       <c r="E4" s="9" t="n"/>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>闭环方式</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -1975,24 +1456,24 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>关联</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>闭环路径</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>系统继承自分析阶段的闭环方法;决定单号前缀</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
+          <t>系统继承</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>闭环单号</t>
+          <t>分析日期</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -2002,24 +1483,24 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>编号</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>闭环单唯一编号</t>
+          <t>分析提交日期</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>系统继承自分析阶段的问题单号/需求单号;前缀:PC-问题单/RC-需求</t>
+          <t>系统取提交分析表单时当前日期</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>关联主诉求单号</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -2029,24 +1510,24 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
+          <t>单据状态</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>系统继承</t>
+          <t>默认『分析中』</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>关联分析单号</t>
+          <t>责任人(工号+姓名)</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2056,78 +1537,488 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
+          <t>人员(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>改进项责任人</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>系统继承自评审阶段填写的责任人</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>二、分析与接纳</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>接纳版本</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>本次接纳的版本号</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>是否接纳为『是』时必填(如 V1.0);不接纳则留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>是否接纳</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>枚举(单选)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>是否接纳该改进项</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>是/否;否→打回评审阶段</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>不接纳理由</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>不接纳的原因说明</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>是否接纳为『否』时必填;接纳则留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>闭环方法</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>枚举(单选)</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>接纳后走哪条闭环</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>是否接纳为『是』时必填;问题单闭环/需求闭环</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>三、分析进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>表格列</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>进展条目序号</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>系统自增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>本条进展内容描述</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>每条可单独提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>本条提交时间</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>系统取提交时当前时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>提交人</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>人员(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>提交人工号与姓名(成对)</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>系统取当前登录人</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>4-闭环单</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>关联:主诉求单号    闭环方式由分析阶段继承,通过即进入验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>字段名</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>填写要求</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>字段类型</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>详细信息</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>特殊要求</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>一、单据信息</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>闭环方式</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>枚举(单选)</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>闭环路径</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>系统继承自分析阶段的闭环方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>关联主诉求单号</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
           <t>关联</t>
         </is>
       </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>所属主诉求单</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>系统继承</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>当前状态</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>枚举(单选)</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>单据状态</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>默认『实施中』</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>责任人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>人员(工号+姓名)</t>
+        </is>
+      </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>承接分析单</t>
+          <t>改进项责任人</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>系统继承</t>
+          <t>系统继承自分析阶段责任人</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>SLA时间</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>日期/时长</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>单据状态</t>
+          <t>闭环完成时限</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>默认『实施中』</t>
+          <t>由闭环责任人填写并可修改</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>责任人(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>改进项责任人</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>系统继承自分析阶段责任人</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>二、进展与自测</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>SLA时间</t>
+          <t>闭环效果自测</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -2137,24 +2028,24 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>日期/时长</t>
+          <t>富文本(可粘贴图片)</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>闭环完成时限</t>
+          <t>自测的闭环效果</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>由闭环责任人填写并可修改</t>
+          <t>支持富文本与粘贴图片</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>二、进展与自测</t>
+          <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -2165,45 +2056,61 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>闭环效果自测</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>表格列</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>进展条目序号</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>系统自增</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>富文本(可粘贴图片)</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>自测的闭环效果</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>支持富文本与粘贴图片</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>本条进展内容描述</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>每条可单独提交</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>提交时间</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -2213,96 +2120,42 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>表格列</t>
+          <t>日期</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>进展条目序号</t>
+          <t>本条提交时间</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>系统自增</t>
+          <t>系统取提交时当前时间</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>提交人</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>长文本</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>本条进展内容描述</t>
+          <t>提交人工号与姓名(成对)</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>每条可单独提交</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>本条提交时间</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>系统取提交时当前时间</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>提交人</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>提交人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>系统取当前登录人</t>
         </is>
@@ -2313,8 +2166,8 @@
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2326,7 +2179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2346,7 +2199,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联:主诉求单号 + 闭环单号    验收人=改进提出人,不可转单</t>
+          <t>关联:主诉求单号    验收人=改进提出人;不通过则打回闭环(截图贴入验收结论)</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2244,7 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>验收单号</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -2401,24 +2254,24 @@
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>编号</t>
+          <t>关联</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>验收单唯一编号</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>格式 AC-YYYY-NNN</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+          <t>系统继承</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>关联主诉求单号</t>
+          <t>验收人</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -2428,24 +2281,23 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>人员(工号+姓名)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>系统继承</t>
-        </is>
+          <t>验收人工号与姓名(成对)</t>
+        </is>
+      </c>
+      <c r="E6" s="12">
+        <f>改进提出人,系统生成,锁定不可转单</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>关联闭环单号</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -2455,133 +2307,80 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>承接的闭环单</t>
+          <t>单据状态</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>系统继承</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>验收人</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>人员(工号+姓名)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>验收人工号与姓名(成对)</t>
-        </is>
-      </c>
-      <c r="E8" s="12">
-        <f>改进提出人,系统生成,锁定不可转单</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
+          <t>默认『待验收』</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>二、验收结论</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>当前状态</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>验收结论</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
+          <t>富文本(可粘贴图片)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>验收结论说明</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>支持富文本与粘贴图片;不通过时截图贴入结论</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>验收是否通过</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
           <t>枚举(单选)</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>单据状态</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>默认『待验收』</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>二、验收结论</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>验收结论</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>富文本(可粘贴图片)</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>验收结论说明</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>支持富文本与粘贴图片;不通过时截图贴入结论</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>验收是否通过</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>枚举(单选)</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>是否通过验收</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>通过/不通过;不通过则打回闭环阶段</t>
         </is>
@@ -2592,7 +2391,7 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/质量改进诉求表单-字段规格审核.xlsx
+++ b/质量改进诉求表单-字段规格审核.xlsx
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1401,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>关联:主诉求单号    接纳后进入闭环;不接纳则打回评审</t>
+          <t>关联:主诉求单号    接纳后填写闭环单号(校验合法性)进入闭环;不接纳则打回评审</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>三、分析进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
+          <t>三、闭环单号(接纳后必填,需校验合法性)</t>
         </is>
       </c>
       <c r="B14" s="9" t="n"/>
@@ -1681,64 +1681,48 @@
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>问题单号/需求单号</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>条件必填</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>表格列</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>进展条目序号</t>
+          <t>闭环对应的单号</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>系统自增</t>
+          <t>是否接纳为『是』时必填;需校验编号合法性(格式正确且单据真实存在),校验通过方可进入闭环阶段</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>长文本</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>本条进展内容描述</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>每条可单独提交</t>
-        </is>
-      </c>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>四、分析进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>提交时间</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1748,51 +1732,106 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>表格列</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>本条提交时间</t>
+          <t>进展条目序号</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>系统取提交时当前时间</t>
+          <t>系统自增</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>长文本</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>本条进展内容描述</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>每条可单独提交</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>本条提交时间</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>系统取提交时当前时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>提交人</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>系统生成</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>人员(工号+姓名)</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>提交人工号与姓名(成对)</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>系统取当前登录人</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A9:E9"/>
@@ -1807,7 +1846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1896,10 +1935,10 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>关联主诉求单号</t>
+          <t>闭环单号</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1909,24 +1948,24 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>关联</t>
+          <t>编号</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>所属主诉求单</t>
+          <t>闭环单唯一编号</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>系统继承</t>
+          <t>系统继承自分析阶段的问题单号/需求单号;前缀:PC-问题单/RC-需求</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>关联主诉求单号</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
@@ -1936,24 +1975,24 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>枚举(单选)</t>
+          <t>关联</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>单据状态</t>
+          <t>所属主诉求单</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>默认『实施中』</t>
+          <t>系统继承</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>责任人(工号+姓名)</t>
+          <t>当前状态</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -1963,199 +2002,226 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>人员(工号+姓名)</t>
+          <t>枚举(单选)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>改进项责任人</t>
+          <t>单据状态</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>系统继承自分析阶段责任人</t>
+          <t>默认『实施中』</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>责任人(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>人员(工号+姓名)</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>改进项责任人</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>系统继承自分析阶段责任人</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>SLA时间</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>日期/时长</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>闭环完成时限</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>由闭环责任人填写并可修改</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>二、进展与自测</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>闭环效果自测</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>富文本(可粘贴图片)</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>自测的闭环效果</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>支持富文本与粘贴图片</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>三、进展子项(可逐条单独提交,作为外部审视进展的依据)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>表格列</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>进展条目序号</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>系统自增</t>
-        </is>
-      </c>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>进展说明</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>必填</t>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>长文本</t>
+          <t>表格列</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>本条进展内容描述</t>
+          <t>进展条目序号</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>每条可单独提交</t>
+          <t>系统自增</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>提交时间</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>系统生成</t>
+          <t>进展说明</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>必填</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>长文本</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>本条提交时间</t>
+          <t>本条进展内容描述</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>系统取提交时当前时间</t>
+          <t>每条可单独提交</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>提交时间</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>系统生成</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>本条提交时间</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>系统取提交时当前时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>提交人</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>系统生成</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>人员(工号+姓名)</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>提交人工号与姓名(成对)</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>系统取当前登录人</t>
         </is>
@@ -2163,11 +2229,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
